--- a/Configs/GameConfig/Datas/实体.xlsx
+++ b/Configs/GameConfig/Datas/实体.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>##var</t>
   </si>
@@ -99,34 +99,13 @@
     <t>优先级</t>
   </si>
   <si>
-    <t>猫猫</t>
-  </si>
-  <si>
-    <t>res://TheGame/Entitys/CatEntity.tscn</t>
+    <t>Wizard</t>
+  </si>
+  <si>
+    <t>res://TheGame/Entitys/Wizard.tscn</t>
   </si>
   <si>
     <t>Actor</t>
-  </si>
-  <si>
-    <t>感叹号</t>
-  </si>
-  <si>
-    <t>res://TheGame/Entitys/GanTanEntity.tscn</t>
-  </si>
-  <si>
-    <t>Bullet</t>
-  </si>
-  <si>
-    <t>愤怒</t>
-  </si>
-  <si>
-    <t>res://TheGame/Entitys/AngerEntity.tscn</t>
-  </si>
-  <si>
-    <t>闪电球</t>
-  </si>
-  <si>
-    <t>res://TheGame/Entitys/LightningBall.tscn</t>
   </si>
 </sst>
 </file>
@@ -134,10 +113,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -645,19 +624,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1415,21 +1394,11 @@
       <c r="N6" s="14"/>
     </row>
     <row r="7" spans="1:36">
-      <c r="B7" s="4">
-        <v>2</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="4">
-        <v>0</v>
-      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="13"/>
       <c r="J7" s="13"/>
@@ -1438,21 +1407,11 @@
       <c r="N7" s="14"/>
     </row>
     <row r="8" spans="1:36">
-      <c r="B8" s="4">
-        <v>3</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="4">
-        <v>0</v>
-      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="13"/>
       <c r="J8" s="13"/>
@@ -1461,21 +1420,11 @@
       <c r="N8" s="14"/>
     </row>
     <row r="9" spans="1:36">
-      <c r="B9" s="4">
-        <v>4</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="4">
-        <v>0</v>
-      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
       <c r="G9" s="4"/>
       <c r="H9" s="13"/>
       <c r="J9" s="13"/>

--- a/Configs/GameConfig/Datas/实体.xlsx
+++ b/Configs/GameConfig/Datas/实体.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\Godot-Project\StartFromZero\Configs\GameConfig\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -106,6 +111,12 @@
   </si>
   <si>
     <t>Actor</t>
+  </si>
+  <si>
+    <t>Bug</t>
+  </si>
+  <si>
+    <t>res://TheGame/Entitys/Bug.tscn</t>
   </si>
 </sst>
 </file>
@@ -1394,11 +1405,21 @@
       <c r="N6" s="14"/>
     </row>
     <row r="7" spans="1:36">
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="B7" s="4">
+        <v>2</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
       <c r="G7" s="4"/>
       <c r="H7" s="13"/>
       <c r="J7" s="13"/>
